--- a/Эталон_20_типов_5_этапов_ДЛЯ_ПРЕПОДАВАТЕЛЯ_с_нормативами.xlsx
+++ b/Эталон_20_типов_5_этапов_ДЛЯ_ПРЕПОДАВАТЕЛЯ_с_нормативами.xlsx
@@ -871,7 +871,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="31.5" customHeight="1" s="12">
       <c r="A3" s="20" t="inlineStr">
         <is>
@@ -1882,7 +1881,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="31.5" customHeight="1" s="12">
       <c r="A3" s="20" t="inlineStr">
         <is>
@@ -2931,7 +2929,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="31.5" customHeight="1" s="12">
       <c r="A3" s="20" t="inlineStr">
         <is>
@@ -3942,7 +3939,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="31.5" customHeight="1" s="12">
       <c r="A3" s="20" t="inlineStr">
         <is>
@@ -4915,7 +4911,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="31.5" customHeight="1" s="12">
       <c r="A3" s="20" t="inlineStr">
         <is>
@@ -5926,7 +5921,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="31.5" customHeight="1" s="12">
       <c r="A3" s="20" t="inlineStr">
         <is>
@@ -6861,7 +6855,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="31.5" customHeight="1" s="12">
       <c r="A3" s="20" t="inlineStr">
         <is>
@@ -7796,7 +7789,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="31.5" customHeight="1" s="12">
       <c r="A3" s="20" t="inlineStr">
         <is>
@@ -8655,7 +8647,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="31.5" customHeight="1" s="12">
       <c r="A3" s="20" t="inlineStr">
         <is>
@@ -9552,7 +9543,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="31.5" customHeight="1" s="12">
       <c r="A3" s="20" t="inlineStr">
         <is>
@@ -10727,7 +10717,7 @@
       </c>
       <c r="D10" s="18" t="inlineStr">
         <is>
-          <t>Приказы ФСТЭК №17/№239</t>
+          <t>Приказы ФСТЭК №117/№239</t>
         </is>
       </c>
       <c r="E10" s="18" t="inlineStr">
@@ -10759,7 +10749,7 @@
       </c>
       <c r="D11" s="18" t="inlineStr">
         <is>
-          <t>Приказы ФСТЭК №17/№21</t>
+          <t>Приказы ФСТЭК №117/№21</t>
         </is>
       </c>
       <c r="E11" s="18" t="inlineStr">
@@ -10791,7 +10781,7 @@
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>Приказы ФСТЭК №17/№21</t>
+          <t>Приказы ФСТЭК №117/№21</t>
         </is>
       </c>
       <c r="E12" s="18" t="inlineStr">
@@ -10823,7 +10813,7 @@
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>Приказы ФСТЭК №17/№239</t>
+          <t>Приказы ФСТЭК №117/№239</t>
         </is>
       </c>
       <c r="E13" s="18" t="inlineStr">
@@ -10855,7 +10845,7 @@
       </c>
       <c r="D14" s="18" t="inlineStr">
         <is>
-          <t>Приказы ФСТЭК №17/№21</t>
+          <t>Приказы ФСТЭК №117/№21</t>
         </is>
       </c>
       <c r="E14" s="18" t="inlineStr">
@@ -10887,7 +10877,7 @@
       </c>
       <c r="D15" s="18" t="inlineStr">
         <is>
-          <t>Приказ ФСТЭК №17; ПКЗ-2005</t>
+          <t>Приказ ФСТЭК №117; ПКЗ-2005</t>
         </is>
       </c>
       <c r="E15" s="18" t="inlineStr">
@@ -10919,7 +10909,7 @@
       </c>
       <c r="D16" s="18" t="inlineStr">
         <is>
-          <t>Приказ ФСТЭК №17; ГОСТ Р 57580</t>
+          <t>Приказ ФСТЭК №117; ГОСТ Р 57580</t>
         </is>
       </c>
       <c r="E16" s="18" t="inlineStr">
@@ -11191,7 +11181,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="31.5" customHeight="1" s="12">
       <c r="A3" s="20" t="inlineStr">
         <is>
@@ -11974,7 +11963,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="31.5" customHeight="1" s="12">
       <c r="A3" s="20" t="inlineStr">
         <is>
@@ -12833,7 +12821,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="31.5" customHeight="1" s="12">
       <c r="A3" s="20" t="inlineStr">
         <is>
@@ -13654,7 +13641,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="31.5" customHeight="1" s="12">
       <c r="A3" s="20" t="inlineStr">
         <is>
@@ -15315,7 +15301,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="31.5" customHeight="1" s="12">
       <c r="A3" s="20" t="inlineStr">
         <is>
@@ -16938,7 +16923,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="31.5" customHeight="1" s="12">
       <c r="A3" s="20" t="inlineStr">
         <is>
@@ -18599,7 +18583,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="31.5" customHeight="1" s="12">
       <c r="A3" s="20" t="inlineStr">
         <is>
@@ -20260,7 +20243,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="31.5" customHeight="1" s="12">
       <c r="A3" s="20" t="inlineStr">
         <is>
@@ -22035,7 +22017,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="31.5" customHeight="1" s="12">
       <c r="A3" s="20" t="inlineStr">
         <is>
@@ -23924,7 +23905,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="31.5" customHeight="1" s="12">
       <c r="A3" s="20" t="inlineStr">
         <is>
